--- a/Name.xlsx
+++ b/Name.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Ztemp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\我的資料_路亞國際學校\02A.電腦課程\魔法大對決(新)99乘法熟練練習\英文\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FC02C0A-FFC0-4C0D-8DBF-8670B2E7E384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{447A978C-80A1-427F-B445-A5A47C4137BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3735C96D-6BE7-4A93-BA24-E971F47BE3F8}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="306">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -952,6 +952,10 @@
   </si>
   <si>
     <t>Dean Huang</t>
+  </si>
+  <si>
+    <t>Teacher</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1341,7 +1345,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8220CC7A-D89C-4BDC-9B42-984196CF6311}">
-  <dimension ref="A1:A308"/>
+  <dimension ref="A1:A309"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.875" bestFit="1" customWidth="1"/>
@@ -2887,6 +2891,11 @@
         <v>304</v>
       </c>
     </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A309" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
